--- a/artifacts/test_reporte_maestro.xlsx
+++ b/artifacts/test_reporte_maestro.xlsx
@@ -113,6 +113,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -123,7 +124,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -672,7 +672,7 @@
           <t>Total Depositado</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
         <v>1000</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -687,7 +687,7 @@
           <t>Total Reembolsado</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -728,7 +728,7 @@
           <t>Costo Total</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="6" t="n">
         <v>205.2631578947368</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -743,8 +743,8 @@
           <t>UTILIDAD ESTIMADA</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
-        <v>1294.736842105263</v>
+      <c r="B19" s="6" t="n">
+        <v>1294.74</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
@@ -765,62 +765,62 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>📅 CRONOGRAMA LOGÍSTICO COMPLETO</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Día</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Servicio / Tour</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Proveedor Sugerido</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>Pax</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -840,7 +840,7 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>City Tour Cusco</t>
         </is>
@@ -866,80 +866,80 @@
       <c r="I25" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>💰 DETALLE DE LIQUIDACIÓN Y PAGOS</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="7" t="n"/>
-      <c r="L28" s="7" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Día</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Proveedor Real</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Tipo Servicio</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Moneda</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>Costo Unit.</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>Cant/Pax</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>Total Línea</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>T.C.</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>Total Gral (USD)</t>
         </is>
       </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="K29" s="8" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>Método Pago</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr">
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>Obs. Contables</t>
         </is>
@@ -949,7 +949,7 @@
       <c r="A30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Hotel Hilton</t>
         </is>
@@ -964,19 +964,19 @@
           <t>PEN</t>
         </is>
       </c>
-      <c r="E30" s="10" t="n">
+      <c r="E30" s="6" t="n">
         <v>200</v>
       </c>
       <c r="F30" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="G30" s="6" t="n">
         <v>400</v>
       </c>
       <c r="H30" s="11" t="n">
         <v>3.8</v>
       </c>
-      <c r="I30" s="10" t="n">
+      <c r="I30" s="6" t="n">
         <v>105.2631578947368</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -999,7 +999,7 @@
       <c r="A31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Machu Picchu Entrance</t>
         </is>
@@ -1014,19 +1014,19 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="6" t="n">
         <v>50</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="10" t="n">
+      <c r="G31" s="6" t="n">
         <v>100</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="10" t="n">
+      <c r="I31" s="6" t="n">
         <v>100</v>
       </c>
       <c r="J31" s="12" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Juan</t>
         </is>
